--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
